--- a/output/graficos_dimensiones/comunal_d_env_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:29</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_biobio.xlsx
@@ -75,12 +75,12 @@
     <t xml:space="preserve">Laja</t>
   </si>
   <si>
+    <t xml:space="preserve">Mulchén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santa Juana</t>
   </si>
   <si>
-    <t xml:space="preserve">Mulchén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
@@ -114,12 +114,12 @@
     <t xml:space="preserve">Coronel</t>
   </si>
   <si>
+    <t xml:space="preserve">Los Angeles</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hualqui</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cañete</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -577,7 +577,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>163.39</v>
+        <v>174.01</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>136.58</v>
+        <v>147.33</v>
       </c>
     </row>
     <row r="4">
@@ -611,7 +611,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>135.75</v>
+        <v>145.8</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>131.4</v>
+        <v>143.41</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>125.35</v>
+        <v>137.42</v>
       </c>
     </row>
     <row r="7">
@@ -662,7 +662,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>124.58</v>
+        <v>133.68</v>
       </c>
     </row>
     <row r="8">
@@ -679,7 +679,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>117.19</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="9">
@@ -696,7 +696,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>116.64</v>
+        <v>125.69</v>
       </c>
     </row>
     <row r="10">
@@ -713,7 +713,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>115.7</v>
+        <v>124.7</v>
       </c>
     </row>
     <row r="11">
@@ -730,7 +730,7 @@
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>111.77</v>
+        <v>120.27</v>
       </c>
     </row>
     <row r="12">
@@ -747,7 +747,7 @@
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>109.72</v>
+        <v>117.89</v>
       </c>
     </row>
     <row r="13">
@@ -764,7 +764,7 @@
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>106.08</v>
+        <v>116.15</v>
       </c>
     </row>
     <row r="14">
@@ -781,7 +781,7 @@
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>105.76</v>
+        <v>113.51</v>
       </c>
     </row>
     <row r="15">
@@ -792,13 +792,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>8109</v>
+        <v>8305</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>105.52</v>
+        <v>112.94</v>
       </c>
     </row>
     <row r="16">
@@ -809,13 +809,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>8305</v>
+        <v>8109</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>104.49</v>
+        <v>111.76</v>
       </c>
     </row>
     <row r="17">
@@ -832,7 +832,7 @@
         <v>2019</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>102.3</v>
+        <v>109.94</v>
       </c>
     </row>
     <row r="18">
@@ -849,7 +849,7 @@
         <v>2019</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>99.98</v>
+        <v>107.94</v>
       </c>
     </row>
     <row r="19">
@@ -866,7 +866,7 @@
         <v>2019</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>99.4</v>
+        <v>107.19</v>
       </c>
     </row>
     <row r="20">
@@ -883,7 +883,7 @@
         <v>2019</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>98.33</v>
+        <v>106.22</v>
       </c>
     </row>
     <row r="21">
@@ -900,7 +900,7 @@
         <v>2019</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>97.63</v>
+        <v>105.13</v>
       </c>
     </row>
     <row r="22">
@@ -917,7 +917,7 @@
         <v>2019</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>96.19</v>
+        <v>103.74</v>
       </c>
     </row>
     <row r="23">
@@ -934,7 +934,7 @@
         <v>2019</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>94.68</v>
+        <v>102.63</v>
       </c>
     </row>
     <row r="24">
@@ -951,7 +951,7 @@
         <v>2019</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>92.46</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="25">
@@ -968,7 +968,7 @@
         <v>2019</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>84.93</v>
+        <v>91.21</v>
       </c>
     </row>
     <row r="26">
@@ -985,7 +985,7 @@
         <v>2019</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>83.42</v>
+        <v>89.53</v>
       </c>
     </row>
     <row r="27">
@@ -1002,7 +1002,7 @@
         <v>2019</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>80.45</v>
+        <v>86.53</v>
       </c>
     </row>
     <row r="28">
@@ -1013,13 +1013,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8105</v>
+        <v>8301</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>80.35</v>
+        <v>86.27</v>
       </c>
     </row>
     <row r="29">
@@ -1030,13 +1030,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>8301</v>
+        <v>8105</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>80.19</v>
+        <v>86.24</v>
       </c>
     </row>
     <row r="30">
@@ -1053,7 +1053,7 @@
         <v>2019</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>77.8</v>
+        <v>84.23</v>
       </c>
     </row>
     <row r="31">
@@ -1070,7 +1070,7 @@
         <v>2019</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>69.94</v>
+        <v>75.44</v>
       </c>
     </row>
     <row r="32">
@@ -1087,7 +1087,7 @@
         <v>2019</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>64.42</v>
+        <v>69.1</v>
       </c>
     </row>
     <row r="33">
@@ -1104,7 +1104,7 @@
         <v>2019</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>60.46</v>
+        <v>64.78</v>
       </c>
     </row>
     <row r="34">
@@ -1121,7 +1121,7 @@
         <v>2019</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>44.43</v>
+        <v>47.49</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:09</t>
+    <t xml:space="preserve">2026-10-02 16:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_biobio.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Coronel</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Hualqui</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Cañete</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:09</t>
+    <t xml:space="preserve">2026-10-04 10:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:38</t>
+    <t xml:space="preserve">2026-10-05 16:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
